--- a/salidas/empresas/T.xlsx
+++ b/salidas/empresas/T.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,54 +447,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>4.995421409606934</v>
+        <v>4.995419025421143</v>
       </c>
       <c r="C3" t="n">
         <v>20.83836936950684</v>
@@ -520,7 +532,7 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>4.824069499969482</v>
+        <v>4.824068069458008</v>
       </c>
       <c r="C5" t="n">
         <v>19.79607391357422</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>4.79646110534668</v>
+        <v>4.796462059020996</v>
       </c>
       <c r="C6" t="n">
         <v>19.68277931213379</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>5.133280277252197</v>
+        <v>5.133283138275146</v>
       </c>
       <c r="C7" t="n">
         <v>21.06495475769043</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>5.608422756195068</v>
+        <v>5.608425617218018</v>
       </c>
       <c r="C8" t="n">
         <v>22.65105628967285</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>5.821616172790527</v>
+        <v>5.821617126464844</v>
       </c>
       <c r="C9" t="n">
         <v>23.5120849609375</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>6.089041233062744</v>
+        <v>6.089038372039795</v>
       </c>
       <c r="C10" t="n">
         <v>24.5921459197998</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>6.49257230758667</v>
+        <v>6.492571353912354</v>
       </c>
       <c r="C11" t="n">
         <v>25.86857986450195</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>6.428118705749512</v>
+        <v>6.428120136260986</v>
       </c>
       <c r="C12" t="n">
         <v>25.61178207397461</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>6.776918888092041</v>
+        <v>6.776917934417725</v>
       </c>
       <c r="C13" t="n">
         <v>27.00151062011719</v>
@@ -710,7 +722,7 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>7.073865413665771</v>
+        <v>7.073863506317139</v>
       </c>
       <c r="C15" t="n">
         <v>27.7945613861084</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>7.579415321350098</v>
+        <v>7.579416275024414</v>
       </c>
       <c r="C16" t="n">
         <v>29.78096771240234</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>7.533195018768311</v>
+        <v>7.533193111419678</v>
       </c>
       <c r="C17" t="n">
         <v>29.24471282958984</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>8.042926788330078</v>
+        <v>8.042928695678711</v>
       </c>
       <c r="C18" t="n">
         <v>31.22356414794922</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>8.074055671691895</v>
+        <v>8.074057579040527</v>
       </c>
       <c r="C19" t="n">
         <v>31.34441184997559</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>7.707234859466553</v>
+        <v>7.707237243652344</v>
       </c>
       <c r="C20" t="n">
         <v>29.57703971862793</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>7.846978664398193</v>
+        <v>7.846974849700928</v>
       </c>
       <c r="C21" t="n">
         <v>30.1132926940918</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>8.327201843261719</v>
+        <v>8.327198028564453</v>
       </c>
       <c r="C22" t="n">
         <v>31.9561939239502</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>8.31796932220459</v>
+        <v>8.317963600158691</v>
       </c>
       <c r="C23" t="n">
         <v>31.56344413757324</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>7.605396747589111</v>
+        <v>7.605394840240479</v>
       </c>
       <c r="C24" t="n">
         <v>28.85951614379883</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>8.272188186645508</v>
+        <v>8.272187232971191</v>
       </c>
       <c r="C25" t="n">
         <v>31.38972854614258</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>7.760328769683838</v>
+        <v>7.760327816009521</v>
       </c>
       <c r="C26" t="n">
         <v>29.07099723815918</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>7.022399425506592</v>
+        <v>7.022404670715332</v>
       </c>
       <c r="C27" t="n">
         <v>26.3066463470459</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>7.722018241882324</v>
+        <v>7.722021102905273</v>
       </c>
       <c r="C28" t="n">
         <v>28.92749214172363</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>7.912099361419678</v>
+        <v>7.912102699279785</v>
       </c>
       <c r="C29" t="n">
         <v>29.23715972900391</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>8.155329704284668</v>
+        <v>8.155331611633301</v>
       </c>
       <c r="C30" t="n">
         <v>30.13595199584961</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>6.886040210723877</v>
+        <v>6.886041164398193</v>
       </c>
       <c r="C31" t="n">
         <v>25.44561958312988</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>6.401121616363525</v>
+        <v>6.401119232177734</v>
       </c>
       <c r="C32" t="n">
         <v>23.27039337158203</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>6.646277904510498</v>
+        <v>6.646279811859131</v>
       </c>
       <c r="C33" t="n">
         <v>24.16163063049316</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>5.800689220428467</v>
+        <v>5.800690174102783</v>
       </c>
       <c r="C34" t="n">
         <v>21.08761215209961</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>5.678599834442139</v>
+        <v>5.678600788116455</v>
       </c>
       <c r="C35" t="n">
         <v>20.21903228759766</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>6.058304786682129</v>
+        <v>6.05830717086792</v>
       </c>
       <c r="C36" t="n">
         <v>21.57099723815918</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>6.045578956604004</v>
+        <v>6.045577526092529</v>
       </c>
       <c r="C37" t="n">
         <v>21.52568054199219</v>
@@ -1166,7 +1178,7 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>5.140835285186768</v>
+        <v>5.140833854675293</v>
       </c>
       <c r="C39" t="n">
         <v>17.95317268371582</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>5.450107574462891</v>
+        <v>5.450106620788574</v>
       </c>
       <c r="C40" t="n">
         <v>19.03323364257812</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>5.656418323516846</v>
+        <v>5.656420707702637</v>
       </c>
       <c r="C41" t="n">
         <v>19.3504524230957</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>5.473170757293701</v>
+        <v>5.473170280456543</v>
       </c>
       <c r="C42" t="n">
         <v>18.72356414794922</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>5.484210968017578</v>
+        <v>5.484211444854736</v>
       </c>
       <c r="C43" t="n">
         <v>18.76132965087891</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>5.923248767852783</v>
+        <v>5.923252582550049</v>
       </c>
       <c r="C44" t="n">
         <v>19.81117820739746</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>5.882605075836182</v>
+        <v>5.882604598999023</v>
       </c>
       <c r="C45" t="n">
         <v>19.67522621154785</v>
@@ -1324,11 +1336,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>6.099390983581543</v>
+        <v>6.099394798278809</v>
       </c>
       <c r="C46" t="n">
         <v>20.40030288696289</v>
@@ -1349,11 +1361,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>5.915060997009277</v>
+        <v>5.915059566497803</v>
       </c>
       <c r="C47" t="n">
         <v>19.38821792602539</v>
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>6.207701206207275</v>
+        <v>6.207700729370117</v>
       </c>
       <c r="C48" t="n">
         <v>20.34743118286133</v>
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>6.45886754989624</v>
+        <v>6.458864688873291</v>
       </c>
       <c r="C49" t="n">
         <v>21.17069435119629</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>5.960165023803711</v>
+        <v>5.960163116455078</v>
       </c>
       <c r="C50" t="n">
         <v>19.15407943725586</v>
@@ -1449,7 +1461,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>6.07297420501709</v>
+        <v>6.072978973388672</v>
       </c>
       <c r="C52" t="n">
         <v>19.51661682128906</v>
@@ -1499,11 +1511,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>6.256926536560059</v>
+        <v>6.256923675537109</v>
       </c>
       <c r="C53" t="n">
         <v>19.68277931213379</v>
@@ -1524,7 +1536,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>5.807941913604736</v>
+        <v>5.807942867279053</v>
       </c>
       <c r="C55" t="n">
         <v>18.27039337158203</v>
@@ -1574,11 +1586,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>6.373300552368164</v>
+        <v>6.373301029205322</v>
       </c>
       <c r="C56" t="n">
         <v>19.5921459197998</v>
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>6.641108989715576</v>
+        <v>6.641111850738525</v>
       </c>
       <c r="C57" t="n">
         <v>20.41540718078613</v>
@@ -1624,11 +1636,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>7.026847839355469</v>
+        <v>7.026848316192627</v>
       </c>
       <c r="C58" t="n">
         <v>21.6012077331543</v>
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>7.14246940612793</v>
+        <v>7.142472267150879</v>
       </c>
       <c r="C59" t="n">
         <v>21.54078483581543</v>
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>6.959651470184326</v>
+        <v>6.959652423858643</v>
       </c>
       <c r="C60" t="n">
         <v>20.98942565917969</v>
@@ -1699,11 +1711,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>7.35784912109375</v>
+        <v>7.357848644256592</v>
       </c>
       <c r="C61" t="n">
         <v>22.19033241271973</v>
@@ -1724,11 +1736,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>7.025446891784668</v>
+        <v>7.025445461273193</v>
       </c>
       <c r="C62" t="n">
         <v>20.78549766540527</v>
@@ -1749,11 +1761,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>7.24498987197876</v>
+        <v>7.244993209838867</v>
       </c>
       <c r="C63" t="n">
         <v>21.43504524230957</v>
@@ -1774,11 +1786,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>7.814276695251465</v>
+        <v>7.814279556274414</v>
       </c>
       <c r="C64" t="n">
         <v>23.11933517456055</v>
@@ -1803,11 +1815,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>8.094585418701172</v>
+        <v>8.094583511352539</v>
       </c>
       <c r="C65" t="n">
         <v>23.50453186035156</v>
@@ -1832,7 +1844,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
@@ -1861,11 +1873,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>8.170015335083008</v>
+        <v>8.170014381408691</v>
       </c>
       <c r="C67" t="n">
         <v>23.72356414794922</v>
@@ -1890,11 +1902,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>7.750280857086182</v>
+        <v>7.750281810760498</v>
       </c>
       <c r="C68" t="n">
         <v>22.09969711303711</v>
@@ -1919,11 +1931,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>7.543679714202881</v>
+        <v>7.543678760528564</v>
       </c>
       <c r="C69" t="n">
         <v>21.51057434082031</v>
@@ -1948,11 +1960,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>7.554273128509521</v>
+        <v>7.554276466369629</v>
       </c>
       <c r="C70" t="n">
         <v>21.54078483581543</v>
@@ -1977,11 +1989,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>7.922856330871582</v>
+        <v>7.922854423522949</v>
       </c>
       <c r="C71" t="n">
         <v>22.1374626159668</v>
@@ -2006,11 +2018,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>7.833653926849365</v>
+        <v>7.833653450012207</v>
       </c>
       <c r="C72" t="n">
         <v>21.88821792602539</v>
@@ -2035,11 +2047,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>8.174245834350586</v>
+        <v>8.17424488067627</v>
       </c>
       <c r="C73" t="n">
         <v>22.83987808227539</v>
@@ -2064,11 +2076,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>8.105207443237305</v>
+        <v>8.105208396911621</v>
       </c>
       <c r="C74" t="n">
         <v>22.21299171447754</v>
@@ -2093,11 +2105,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>8.430410385131836</v>
+        <v>8.430408477783203</v>
       </c>
       <c r="C75" t="n">
         <v>23.1042308807373</v>
@@ -2122,7 +2134,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
@@ -2151,7 +2163,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
@@ -2180,11 +2192,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>9.594073295593262</v>
+        <v>9.594074249267578</v>
       </c>
       <c r="C78" t="n">
         <v>25.80815696716309</v>
@@ -2209,11 +2221,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>10.01242446899414</v>
+        <v>10.01242828369141</v>
       </c>
       <c r="C79" t="n">
         <v>26.93353462219238</v>
@@ -2238,11 +2250,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>10.82324886322021</v>
+        <v>10.8232479095459</v>
       </c>
       <c r="C80" t="n">
         <v>28.64048385620117</v>
@@ -2267,11 +2279,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>10.45790767669678</v>
+        <v>10.45790958404541</v>
       </c>
       <c r="C81" t="n">
         <v>27.67371559143066</v>
@@ -2296,11 +2308,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>10.76045417785645</v>
+        <v>10.76045799255371</v>
       </c>
       <c r="C82" t="n">
         <v>28.47431945800781</v>
@@ -2325,11 +2337,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>10.02511692047119</v>
+        <v>10.02511596679688</v>
       </c>
       <c r="C83" t="n">
         <v>26.1253776550293</v>
@@ -2354,11 +2366,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>9.89179801940918</v>
+        <v>9.891796112060547</v>
       </c>
       <c r="C84" t="n">
         <v>25.77794647216797</v>
@@ -2383,11 +2395,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>9.770071983337402</v>
+        <v>9.770069122314453</v>
       </c>
       <c r="C85" t="n">
         <v>25.46072578430176</v>
@@ -2412,11 +2424,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>10.25574398040771</v>
+        <v>10.2557430267334</v>
       </c>
       <c r="C86" t="n">
         <v>26.27643585205078</v>
@@ -2441,7 +2453,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
@@ -2470,11 +2482,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>10.81584167480469</v>
+        <v>10.81583786010742</v>
       </c>
       <c r="C88" t="n">
         <v>27.71147918701172</v>
@@ -2499,11 +2511,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>11.2186336517334</v>
+        <v>11.21863651275635</v>
       </c>
       <c r="C89" t="n">
         <v>28.29305076599121</v>
@@ -2528,11 +2540,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>10.47891044616699</v>
+        <v>10.47891235351562</v>
       </c>
       <c r="C90" t="n">
         <v>26.42749214172363</v>
@@ -2557,11 +2569,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>10.60169887542725</v>
+        <v>10.60169696807861</v>
       </c>
       <c r="C91" t="n">
         <v>26.73715972900391</v>
@@ -2586,11 +2598,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>10.74137783050537</v>
+        <v>10.74137878417969</v>
       </c>
       <c r="C92" t="n">
         <v>26.63897323608398</v>
@@ -2615,11 +2627,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>10.30282878875732</v>
+        <v>10.30283260345459</v>
       </c>
       <c r="C93" t="n">
         <v>25.55135917663574</v>
@@ -2644,11 +2656,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>10.29978275299072</v>
+        <v>10.29978656768799</v>
       </c>
       <c r="C94" t="n">
         <v>25.5438060760498</v>
@@ -2673,11 +2685,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>11.22124576568604</v>
+        <v>11.22124290466309</v>
       </c>
       <c r="C95" t="n">
         <v>27.34139060974121</v>
@@ -2702,11 +2714,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>10.91436672210693</v>
+        <v>10.91436576843262</v>
       </c>
       <c r="C96" t="n">
         <v>26.59365653991699</v>
@@ -2731,11 +2743,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>10.8988676071167</v>
+        <v>10.89886665344238</v>
       </c>
       <c r="C97" t="n">
         <v>26.5558910369873</v>
@@ -2760,11 +2772,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>10.51168060302734</v>
+        <v>10.51167869567871</v>
       </c>
       <c r="C98" t="n">
         <v>25.16616249084473</v>
@@ -2789,11 +2801,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>10.07316780090332</v>
+        <v>10.07317066192627</v>
       </c>
       <c r="C99" t="n">
         <v>24.11631393432617</v>
@@ -2818,11 +2830,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>11.06376552581787</v>
+        <v>11.06376075744629</v>
       </c>
       <c r="C100" t="n">
         <v>26.4879150390625</v>
@@ -2847,11 +2859,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>11.45916271209717</v>
+        <v>11.45916843414307</v>
       </c>
       <c r="C101" t="n">
         <v>26.9637451171875</v>
@@ -2876,7 +2888,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
@@ -2905,11 +2917,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>11.35002994537354</v>
+        <v>11.35002708435059</v>
       </c>
       <c r="C103" t="n">
         <v>26.70694923400879</v>
@@ -2934,7 +2946,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
@@ -2963,11 +2975,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>11.41463661193848</v>
+        <v>11.41463851928711</v>
       </c>
       <c r="C105" t="n">
         <v>26.40483474731445</v>
@@ -2992,11 +3004,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>11.5060567855835</v>
+        <v>11.50606060028076</v>
       </c>
       <c r="C106" t="n">
         <v>26.61631393432617</v>
@@ -3021,11 +3033,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>11.57499885559082</v>
+        <v>11.57499217987061</v>
       </c>
       <c r="C107" t="n">
         <v>26.31419944763184</v>
@@ -3050,11 +3062,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>11.75440406799316</v>
+        <v>11.75439929962158</v>
       </c>
       <c r="C108" t="n">
         <v>26.72205352783203</v>
@@ -3079,11 +3091,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>11.15970420837402</v>
+        <v>11.15970706939697</v>
       </c>
       <c r="C109" t="n">
         <v>25.37009048461914</v>
@@ -3108,11 +3120,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>11.1434850692749</v>
+        <v>11.14348697662354</v>
       </c>
       <c r="C110" t="n">
         <v>24.86404800415039</v>
@@ -3137,11 +3149,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>11.69863414764404</v>
+        <v>11.69863033294678</v>
       </c>
       <c r="C111" t="n">
         <v>26.10271835327148</v>
@@ -3166,7 +3178,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
@@ -3195,11 +3207,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>11.94995975494385</v>
+        <v>11.94996356964111</v>
       </c>
       <c r="C113" t="n">
         <v>26.16314125061035</v>
@@ -3224,11 +3236,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>11.9154691696167</v>
+        <v>11.91546154022217</v>
       </c>
       <c r="C114" t="n">
         <v>26.08761215209961</v>
@@ -3253,11 +3265,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>12.25354480743408</v>
+        <v>12.25354099273682</v>
       </c>
       <c r="C115" t="n">
         <v>26.82779502868652</v>
@@ -3282,11 +3294,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>12.1966381072998</v>
+        <v>12.19664096832275</v>
       </c>
       <c r="C116" t="n">
         <v>26.23867034912109</v>
@@ -3311,11 +3323,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>11.65597248077393</v>
+        <v>11.65597343444824</v>
       </c>
       <c r="C117" t="n">
         <v>25.07552909851074</v>
@@ -3340,11 +3352,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>11.43830299377441</v>
+        <v>11.43830394744873</v>
       </c>
       <c r="C118" t="n">
         <v>24.60725021362305</v>
@@ -3369,11 +3381,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>11.9887809753418</v>
+        <v>11.98878192901611</v>
       </c>
       <c r="C119" t="n">
         <v>25.30966758728027</v>
@@ -3398,11 +3410,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>12.04601764678955</v>
+        <v>12.04602527618408</v>
       </c>
       <c r="C120" t="n">
         <v>25.43051338195801</v>
@@ -3427,11 +3439,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>12.31076812744141</v>
+        <v>12.31077194213867</v>
       </c>
       <c r="C121" t="n">
         <v>25.98942565917969</v>
@@ -3456,11 +3468,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>13.14255619049072</v>
+        <v>13.14255237579346</v>
       </c>
       <c r="C122" t="n">
         <v>27.23564910888672</v>
@@ -3485,11 +3497,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>13.46692180633545</v>
+        <v>13.46692085266113</v>
       </c>
       <c r="C123" t="n">
         <v>27.9078540802002</v>
@@ -3514,11 +3526,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>14.27603435516357</v>
+        <v>14.27603530883789</v>
       </c>
       <c r="C124" t="n">
         <v>29.58459281921387</v>
@@ -3543,11 +3555,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>14.38168907165527</v>
+        <v>14.38169574737549</v>
       </c>
       <c r="C125" t="n">
         <v>29.32024192810059</v>
@@ -3572,11 +3584,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>14.50394535064697</v>
+        <v>14.50395011901855</v>
       </c>
       <c r="C126" t="n">
         <v>29.56948661804199</v>
@@ -3601,11 +3613,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>16.008056640625</v>
+        <v>16.00806617736816</v>
       </c>
       <c r="C127" t="n">
         <v>32.63595199584961</v>
@@ -3630,11 +3642,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>16.27631568908691</v>
+        <v>16.27631187438965</v>
       </c>
       <c r="C128" t="n">
         <v>32.69637680053711</v>
@@ -3659,7 +3671,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
@@ -3688,7 +3700,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
@@ -3717,11 +3729,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>14.05630397796631</v>
+        <v>14.05630683898926</v>
       </c>
       <c r="C131" t="n">
         <v>27.78700828552246</v>
@@ -3746,11 +3758,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>14.75931072235107</v>
+        <v>14.75930690765381</v>
       </c>
       <c r="C132" t="n">
         <v>29.17673683166504</v>
@@ -3775,11 +3787,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>16.2493782043457</v>
+        <v>16.24937438964844</v>
       </c>
       <c r="C133" t="n">
         <v>32.12235641479492</v>
@@ -3804,11 +3816,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>16.35682106018066</v>
+        <v>16.3568172454834</v>
       </c>
       <c r="C134" t="n">
         <v>31.84289932250977</v>
@@ -3833,11 +3845,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>16.21327590942383</v>
+        <v>16.21327209472656</v>
       </c>
       <c r="C135" t="n">
         <v>31.56344413757324</v>
@@ -3862,7 +3874,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
@@ -3891,11 +3903,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>15.61937427520752</v>
+        <v>15.61937141418457</v>
       </c>
       <c r="C137" t="n">
         <v>29.9320240020752</v>
@@ -3920,11 +3932,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>15.18583106994629</v>
+        <v>15.18582820892334</v>
       </c>
       <c r="C138" t="n">
         <v>29.1012077331543</v>
@@ -3949,7 +3961,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
@@ -3974,11 +3986,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>15.63719654083252</v>
+        <v>15.63719940185547</v>
       </c>
       <c r="C140" t="n">
         <v>29.4561939239502</v>
@@ -3999,11 +4011,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>15.01972961425781</v>
+        <v>15.01972770690918</v>
       </c>
       <c r="C141" t="n">
         <v>28.29305076599121</v>
@@ -4024,11 +4036,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>15.70536518096924</v>
+        <v>15.70535850524902</v>
       </c>
       <c r="C142" t="n">
         <v>29.58459281921387</v>
@@ -4049,11 +4061,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>13.71733665466309</v>
+        <v>13.71733570098877</v>
       </c>
       <c r="C143" t="n">
         <v>25.41540718078613</v>
@@ -4074,11 +4086,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>14.83021354675293</v>
+        <v>14.83021640777588</v>
       </c>
       <c r="C144" t="n">
         <v>27.47734069824219</v>
@@ -4099,11 +4111,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>15.84933471679688</v>
+        <v>15.84933376312256</v>
       </c>
       <c r="C145" t="n">
         <v>29.36555862426758</v>
@@ -4124,11 +4136,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>15.53527164459229</v>
+        <v>15.53526496887207</v>
       </c>
       <c r="C146" t="n">
         <v>28.28549766540527</v>
@@ -4149,11 +4161,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>15.0582160949707</v>
+        <v>15.05821514129639</v>
       </c>
       <c r="C147" t="n">
         <v>27.41691780090332</v>
@@ -4178,11 +4190,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>14.78858280181885</v>
+        <v>14.78857803344727</v>
       </c>
       <c r="C148" t="n">
         <v>26.92598152160645</v>
@@ -4207,11 +4219,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>13.82164478302002</v>
+        <v>13.82164573669434</v>
       </c>
       <c r="C149" t="n">
         <v>24.69788551330566</v>
@@ -4236,11 +4248,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>13.66102313995361</v>
+        <v>13.66102600097656</v>
       </c>
       <c r="C150" t="n">
         <v>24.41087532043457</v>
@@ -4265,7 +4277,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
@@ -4294,11 +4306,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>13.79248332977295</v>
+        <v>13.79248428344727</v>
       </c>
       <c r="C152" t="n">
         <v>24.14652633666992</v>
@@ -4323,11 +4335,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>13.77954196929932</v>
+        <v>13.77953815460205</v>
       </c>
       <c r="C153" t="n">
         <v>24.12386703491211</v>
@@ -4352,11 +4364,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>14.48706817626953</v>
+        <v>14.48707008361816</v>
       </c>
       <c r="C154" t="n">
         <v>25.3625373840332</v>
@@ -4381,11 +4393,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>13.4979133605957</v>
+        <v>13.4979190826416</v>
       </c>
       <c r="C155" t="n">
         <v>23.17220497131348</v>
@@ -4410,11 +4422,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>13.74429225921631</v>
+        <v>13.74429512023926</v>
       </c>
       <c r="C156" t="n">
         <v>23.59516525268555</v>
@@ -4439,7 +4451,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
@@ -4468,11 +4480,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>13.51693153381348</v>
+        <v>13.51693058013916</v>
       </c>
       <c r="C158" t="n">
         <v>22.70392608642578</v>
@@ -4497,7 +4509,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
@@ -4526,11 +4538,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>14.1014986038208</v>
+        <v>14.10149478912354</v>
       </c>
       <c r="C160" t="n">
         <v>23.68580055236816</v>
@@ -4555,11 +4567,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>14.21803760528564</v>
+        <v>14.21803855895996</v>
       </c>
       <c r="C161" t="n">
         <v>23.38368606567383</v>
@@ -4584,11 +4596,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>14.04352855682373</v>
+        <v>14.04352569580078</v>
       </c>
       <c r="C162" t="n">
         <v>23.09667778015137</v>
@@ -4613,11 +4625,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>15.38909530639648</v>
+        <v>15.38909244537354</v>
       </c>
       <c r="C163" t="n">
         <v>25.30966758728027</v>
@@ -4642,11 +4654,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>15.95157241821289</v>
+        <v>15.95157337188721</v>
       </c>
       <c r="C164" t="n">
         <v>25.7175235748291</v>
@@ -4671,11 +4683,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>16.5184211730957</v>
+        <v>16.51842308044434</v>
       </c>
       <c r="C165" t="n">
         <v>26.63142013549805</v>
@@ -4700,11 +4712,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>17.72708702087402</v>
+        <v>17.72709083557129</v>
       </c>
       <c r="C166" t="n">
         <v>28.58005905151367</v>
@@ -4729,11 +4741,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>18.36241340637207</v>
+        <v>18.36241722106934</v>
       </c>
       <c r="C167" t="n">
         <v>29.07099723815918</v>
@@ -4758,11 +4770,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>17.8328685760498</v>
+        <v>17.83286666870117</v>
       </c>
       <c r="C168" t="n">
         <v>28.23262786865234</v>
@@ -4787,7 +4799,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
@@ -4816,7 +4828,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
@@ -4845,11 +4857,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>17.1014575958252</v>
+        <v>17.10145378112793</v>
       </c>
       <c r="C171" t="n">
         <v>26.6012077331543</v>
@@ -4874,11 +4886,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>14.15410232543945</v>
+        <v>14.15410327911377</v>
       </c>
       <c r="C172" t="n">
         <v>22.01661682128906</v>
@@ -4903,7 +4915,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
@@ -4932,11 +4944,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>15.33541774749756</v>
+        <v>15.33541584014893</v>
       </c>
       <c r="C174" t="n">
         <v>23.30815696716309</v>
@@ -4961,7 +4973,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -4990,11 +5002,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>15.03926753997803</v>
+        <v>15.03926944732666</v>
       </c>
       <c r="C176" t="n">
         <v>22.34139060974121</v>
@@ -5019,11 +5031,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>15.15620422363281</v>
+        <v>15.15620231628418</v>
       </c>
       <c r="C177" t="n">
         <v>22.51510620117188</v>
@@ -5048,7 +5060,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
@@ -5077,11 +5089,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>14.074143409729</v>
+        <v>14.07414245605469</v>
       </c>
       <c r="C179" t="n">
         <v>20.4078540802002</v>
@@ -5106,7 +5118,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -5135,7 +5147,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
@@ -5164,11 +5176,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>15.26411247253418</v>
+        <v>15.26411628723145</v>
       </c>
       <c r="C182" t="n">
         <v>21.62386703491211</v>
@@ -5193,7 +5205,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
@@ -5220,11 +5232,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>16.13847541809082</v>
+        <v>16.13848304748535</v>
       </c>
       <c r="C184" t="n">
         <v>22.8625373840332</v>
@@ -5247,7 +5259,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
@@ -5274,11 +5286,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>16.04784774780273</v>
+        <v>16.04784965515137</v>
       </c>
       <c r="C186" t="n">
         <v>22.22809791564941</v>
@@ -5301,11 +5313,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>15.69341278076172</v>
+        <v>15.69340896606445</v>
       </c>
       <c r="C187" t="n">
         <v>21.73715972900391</v>
@@ -5328,11 +5340,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>15.6682243347168</v>
+        <v>15.66822624206543</v>
       </c>
       <c r="C188" t="n">
         <v>21.18580055236816</v>
@@ -5355,11 +5367,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>15.31631469726562</v>
+        <v>15.31631565093994</v>
       </c>
       <c r="C189" t="n">
         <v>20.70997047424316</v>
@@ -5382,11 +5394,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>15.08730030059814</v>
+        <v>15.08729934692383</v>
       </c>
       <c r="C190" t="n">
         <v>20.40030288696289</v>
@@ -5409,11 +5421,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>14.47468280792236</v>
+        <v>14.47468376159668</v>
       </c>
       <c r="C191" t="n">
         <v>19.07855033874512</v>
@@ -5436,11 +5448,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>13.08222389221191</v>
+        <v>13.08222579956055</v>
       </c>
       <c r="C192" t="n">
         <v>17.24320220947266</v>
@@ -5465,11 +5477,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>14.09648323059082</v>
+        <v>14.09648418426514</v>
       </c>
       <c r="C193" t="n">
         <v>18.58005905151367</v>
@@ -5494,11 +5506,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>15.0079460144043</v>
+        <v>15.00794410705566</v>
       </c>
       <c r="C194" t="n">
         <v>19.25981903076172</v>
@@ -5523,11 +5535,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>13.94267559051514</v>
+        <v>13.94267463684082</v>
       </c>
       <c r="C195" t="n">
         <v>17.89274978637695</v>
@@ -5552,11 +5564,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>13.90736293792725</v>
+        <v>13.9073600769043</v>
       </c>
       <c r="C196" t="n">
         <v>17.84743118286133</v>
@@ -5581,11 +5593,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>14.90828323364258</v>
+        <v>14.90828037261963</v>
       </c>
       <c r="C197" t="n">
         <v>18.86000061035156</v>
@@ -5610,11 +5622,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>16.82912635803223</v>
+        <v>16.8291187286377</v>
       </c>
       <c r="C198" t="n">
         <v>21.29000091552734</v>
@@ -5639,7 +5651,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -5668,11 +5680,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>15.04276371002197</v>
+        <v>15.04276466369629</v>
       </c>
       <c r="C200" t="n">
         <v>18.78000068664551</v>
@@ -5697,11 +5709,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>14.04953002929688</v>
+        <v>14.04952812194824</v>
       </c>
       <c r="C201" t="n">
         <v>17.54000091552734</v>
@@ -5726,11 +5738,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>12.28732967376709</v>
+        <v>12.28732872009277</v>
       </c>
       <c r="C202" t="n">
         <v>15.34000015258789</v>
@@ -5755,11 +5767,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>14.86157321929932</v>
+        <v>14.86157417297363</v>
       </c>
       <c r="C203" t="n">
         <v>18.22999954223633</v>
@@ -5784,11 +5796,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>15.71755599975586</v>
+        <v>15.71755981445312</v>
       </c>
       <c r="C204" t="n">
         <v>19.28000068664551</v>
@@ -5813,11 +5825,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>15.00831604003906</v>
+        <v>15.00831127166748</v>
       </c>
       <c r="C205" t="n">
         <v>18.40999984741211</v>
@@ -5842,7 +5854,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5871,11 +5883,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>15.63853168487549</v>
+        <v>15.6385326385498</v>
       </c>
       <c r="C207" t="n">
         <v>18.90999984741211</v>
@@ -5898,11 +5910,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>15.91971302032471</v>
+        <v>15.91971206665039</v>
       </c>
       <c r="C208" t="n">
         <v>19.25</v>
@@ -5925,11 +5937,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>14.82029819488525</v>
+        <v>14.82029914855957</v>
       </c>
       <c r="C209" t="n">
         <v>17.67000007629395</v>
@@ -5952,7 +5964,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -5979,11 +5991,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>13.37768936157227</v>
+        <v>13.3776912689209</v>
       </c>
       <c r="C211" t="n">
         <v>15.94999980926514</v>
@@ -6006,7 +6018,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -6033,11 +6045,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>12.62594032287598</v>
+        <v>12.62593936920166</v>
       </c>
       <c r="C213" t="n">
         <v>14.78999996185303</v>
@@ -6060,7 +6072,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6087,11 +6099,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>13.39783763885498</v>
+        <v>13.39783668518066</v>
       </c>
       <c r="C215" t="n">
         <v>15.39999961853027</v>
@@ -6114,11 +6126,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>14.41572380065918</v>
+        <v>14.41572570800781</v>
       </c>
       <c r="C216" t="n">
         <v>16.56999969482422</v>
@@ -6141,7 +6153,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6168,11 +6180,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>15.6411657333374</v>
+        <v>15.64116764068604</v>
       </c>
       <c r="C218" t="n">
         <v>17.69000053405762</v>
@@ -6195,11 +6207,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>14.96919059753418</v>
+        <v>14.96918964385986</v>
       </c>
       <c r="C219" t="n">
         <v>16.93000030517578</v>
@@ -6224,11 +6236,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>15.56158924102783</v>
+        <v>15.56159210205078</v>
       </c>
       <c r="C220" t="n">
         <v>17.60000038146973</v>
@@ -6253,7 +6265,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6282,7 +6294,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6311,11 +6323,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>17.1734733581543</v>
+        <v>17.17347145080566</v>
       </c>
       <c r="C223" t="n">
         <v>19.11000061035156</v>
@@ -6340,11 +6352,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>17.55893325805664</v>
+        <v>17.55893516540527</v>
       </c>
       <c r="C224" t="n">
         <v>19.25</v>
@@ -6369,11 +6381,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>18.15183067321777</v>
+        <v>18.15182876586914</v>
       </c>
       <c r="C225" t="n">
         <v>19.89999961853027</v>
@@ -6398,11 +6410,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>20.06735038757324</v>
+        <v>20.06735420227051</v>
       </c>
       <c r="C226" t="n">
         <v>22</v>
@@ -6427,11 +6439,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>20.82389259338379</v>
+        <v>20.82389640808105</v>
       </c>
       <c r="C227" t="n">
         <v>22.54000091552734</v>
@@ -6456,11 +6468,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>21.39668655395508</v>
+        <v>21.39668846130371</v>
       </c>
       <c r="C228" t="n">
         <v>23.15999984741211</v>
@@ -6485,11 +6497,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>21.03638076782227</v>
+        <v>21.03638458251953</v>
       </c>
       <c r="C229" t="n">
         <v>22.77000045776367</v>
@@ -6514,11 +6526,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>22.20156288146973</v>
+        <v>22.20155906677246</v>
       </c>
       <c r="C230" t="n">
         <v>23.72999954223633</v>
@@ -6543,7 +6555,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6572,7 +6584,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6601,11 +6613,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>26.19092559814453</v>
+        <v>26.1909236907959</v>
       </c>
       <c r="C233" t="n">
         <v>27.70000076293945</v>
@@ -6630,7 +6642,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6659,7 +6671,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6688,11 +6700,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>26.17568588256836</v>
+        <v>26.17568397521973</v>
       </c>
       <c r="C236" t="n">
         <v>27.40999984741211</v>
@@ -6717,11 +6729,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>27.97102546691895</v>
+        <v>27.97102737426758</v>
       </c>
       <c r="C237" t="n">
         <v>29.29000091552734</v>
@@ -6746,7 +6758,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6775,11 +6787,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>23.88992881774902</v>
+        <v>23.88992691040039</v>
       </c>
       <c r="C239" t="n">
         <v>24.75</v>
@@ -6804,7 +6816,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6833,7 +6845,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6862,7 +6874,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6891,7 +6903,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6920,7 +6932,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6949,7 +6961,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -6978,7 +6990,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7007,7 +7019,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7036,7 +7048,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7065,7 +7077,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7094,32 +7106,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>25.29999923706055</v>
+        <v>25.45000076293945</v>
       </c>
       <c r="C250" t="n">
-        <v>25.29999923706055</v>
+        <v>25.45000076293945</v>
       </c>
       <c r="D250" t="n">
-        <v>643952400</v>
+        <v>678168800</v>
       </c>
       <c r="E250" t="n">
         <v>3.010000000000001</v>
       </c>
       <c r="F250" t="n">
-        <v>8.405315361149681</v>
+        <v>8.455149755129385</v>
       </c>
       <c r="G250" t="n">
         <v>6852385650</v>
       </c>
       <c r="H250" t="n">
-        <v>173365351717.0446</v>
+        <v>174393220020.4554</v>
       </c>
       <c r="I250" t="n">
-        <v>0.09397492098244646</v>
+        <v>0.09896827683654962</v>
       </c>
     </row>
   </sheetData>
@@ -7151,75 +7163,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40030</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7255,13 +7267,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40122</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7297,13 +7309,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40304</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7339,13 +7351,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40030</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7381,13 +7393,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40122</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7423,13 +7435,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7456,7 +7468,7 @@
       <c r="I7" t="n">
         <v>1.563444108761329</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="K7" t="n">
@@ -7469,13 +7481,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40304</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7502,7 +7514,7 @@
       <c r="I8" t="n">
         <v>1.48036253776435</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="K8" t="n">
@@ -7515,13 +7527,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7548,7 +7560,7 @@
       <c r="I9" t="n">
         <v>1.586102719033232</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="K9" t="n">
@@ -7561,13 +7573,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7594,7 +7606,7 @@
       <c r="I10" t="n">
         <v>2.749244712990937</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="K10" t="n">
@@ -7607,13 +7619,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7640,7 +7652,7 @@
       <c r="I11" t="n">
         <v>2.537764350453172</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="K11" t="n">
@@ -7653,13 +7665,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7686,7 +7698,7 @@
       <c r="I12" t="n">
         <v>2.651057401812689</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="K12" t="n">
@@ -7699,13 +7711,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7732,7 +7744,7 @@
       <c r="I13" t="n">
         <v>2.590634441087613</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="K13" t="n">
@@ -7745,13 +7757,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7778,7 +7790,7 @@
       <c r="I14" t="n">
         <v>1.480362537764351</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="K14" t="n">
@@ -7791,13 +7803,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7824,7 +7836,7 @@
       <c r="I15" t="n">
         <v>0.4984894259818731</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="K15" t="n">
@@ -7837,13 +7849,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41033</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7870,7 +7882,7 @@
       <c r="I16" t="n">
         <v>0.5211480362537765</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41033</v>
       </c>
       <c r="K16" t="n">
@@ -7883,13 +7895,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41124</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7916,7 +7928,7 @@
       <c r="I17" t="n">
         <v>0.5664652567975832</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41124</v>
       </c>
       <c r="K17" t="n">
@@ -7929,13 +7941,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7962,7 +7974,7 @@
       <c r="I18" t="n">
         <v>0.5815709969788521</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="K18" t="n">
@@ -7975,13 +7987,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8008,7 +8020,7 @@
       <c r="I19" t="n">
         <v>0.9138972809667675</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="K19" t="n">
@@ -8021,13 +8033,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41397</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8054,7 +8066,7 @@
       <c r="I20" t="n">
         <v>0.9667673716012086</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41397</v>
       </c>
       <c r="K20" t="n">
@@ -8067,13 +8079,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41488</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8100,7 +8112,7 @@
       <c r="I21" t="n">
         <v>1.004531722054381</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41488</v>
       </c>
       <c r="K21" t="n">
@@ -8113,13 +8125,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8146,7 +8158,7 @@
       <c r="I22" t="n">
         <v>1.072507552870091</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="K22" t="n">
@@ -8159,13 +8171,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41691</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8192,7 +8204,7 @@
       <c r="I23" t="n">
         <v>2.575528700906345</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41691</v>
       </c>
       <c r="K23" t="n">
@@ -8205,13 +8217,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41761</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8238,7 +8250,7 @@
       <c r="I24" t="n">
         <v>2.598187311178248</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41761</v>
       </c>
       <c r="K24" t="n">
@@ -8251,13 +8263,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8284,7 +8296,7 @@
       <c r="I25" t="n">
         <v>2.575528700906345</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="K25" t="n">
@@ -8297,13 +8309,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41953</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8330,7 +8342,7 @@
       <c r="I26" t="n">
         <v>2.469788519637463</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41953</v>
       </c>
       <c r="K26" t="n">
@@ -8343,13 +8355,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8376,7 +8388,7 @@
       <c r="I27" t="n">
         <v>0.8987915407854987</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="K27" t="n">
@@ -8389,13 +8401,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42129</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8422,7 +8434,7 @@
       <c r="I28" t="n">
         <v>0.8308157099697888</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42129</v>
       </c>
       <c r="K28" t="n">
@@ -8435,13 +8447,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42223</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8468,7 +8480,7 @@
       <c r="I29" t="n">
         <v>0.7552870090634443</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42223</v>
       </c>
       <c r="K29" t="n">
@@ -8481,13 +8493,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42314</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8514,7 +8526,7 @@
       <c r="I30" t="n">
         <v>0.6948640483383688</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42314</v>
       </c>
       <c r="K30" t="n">
@@ -8527,13 +8539,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42418</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8560,7 +8572,7 @@
       <c r="I31" t="n">
         <v>1.767371601208459</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42418</v>
       </c>
       <c r="K31" t="n">
@@ -8573,13 +8585,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8606,7 +8618,7 @@
       <c r="I32" t="n">
         <v>1.767371601208459</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="K32" t="n">
@@ -8619,13 +8631,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42586</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8652,7 +8664,7 @@
       <c r="I33" t="n">
         <v>1.744712990936556</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42586</v>
       </c>
       <c r="K33" t="n">
@@ -8665,13 +8677,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8698,7 +8710,7 @@
       <c r="I34" t="n">
         <v>1.774924471299094</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="K34" t="n">
@@ -8711,13 +8723,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>43151</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8744,7 +8756,7 @@
       <c r="I35" t="n">
         <v>1.578549848942598</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>43151</v>
       </c>
       <c r="K35" t="n">
@@ -8757,13 +8769,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8790,7 +8802,7 @@
       <c r="I36" t="n">
         <v>1.540785498489426</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>43151</v>
       </c>
       <c r="K36" t="n">
@@ -8803,13 +8815,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8836,7 +8848,7 @@
       <c r="I37" t="n">
         <v>1.601208459214502</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43151</v>
       </c>
       <c r="K37" t="n">
@@ -8849,13 +8861,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43042</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8882,7 +8894,7 @@
       <c r="I38" t="n">
         <v>1.56344410876133</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43151</v>
       </c>
       <c r="K38" t="n">
@@ -8895,13 +8907,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43151</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8928,7 +8940,7 @@
       <c r="I39" t="n">
         <v>3.595166163141994</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43151</v>
       </c>
       <c r="K39" t="n">
@@ -8941,13 +8953,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8974,7 +8986,7 @@
       <c r="I40" t="n">
         <v>3.738670694864049</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="K40" t="n">
@@ -8987,13 +8999,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9020,7 +9032,7 @@
       <c r="I41" t="n">
         <v>3.874622356495468</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="K41" t="n">
@@ -9033,13 +9045,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43406</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9066,7 +9078,7 @@
       <c r="I42" t="n">
         <v>3.99546827794562</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43406</v>
       </c>
       <c r="K42" t="n">
@@ -9079,13 +9091,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43516</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9112,7 +9124,7 @@
       <c r="I43" t="n">
         <v>2.167673716012085</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43516</v>
       </c>
       <c r="K43" t="n">
@@ -9125,13 +9137,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43591</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9158,7 +9170,7 @@
       <c r="I44" t="n">
         <v>2.02416918429003</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43591</v>
       </c>
       <c r="K44" t="n">
@@ -9171,13 +9183,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43682</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9204,7 +9216,7 @@
       <c r="I45" t="n">
         <v>1.797583081570997</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43682</v>
       </c>
       <c r="K45" t="n">
@@ -9217,13 +9229,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43774</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9250,7 +9262,7 @@
       <c r="I46" t="n">
         <v>1.684290030211481</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43774</v>
       </c>
       <c r="K46" t="n">
@@ -9263,13 +9275,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43881</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9296,7 +9308,7 @@
       <c r="I47" t="n">
         <v>1.435045317220544</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43881</v>
       </c>
       <c r="K47" t="n">
@@ -9309,13 +9321,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9342,7 +9354,7 @@
       <c r="I48" t="n">
         <v>1.487915407854985</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="K48" t="n">
@@ -9355,13 +9367,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9388,7 +9400,7 @@
       <c r="I49" t="n">
         <v>1.231117824773414</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="K49" t="n">
@@ -9401,13 +9413,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9434,7 +9446,7 @@
       <c r="I50" t="n">
         <v>1.148036253776435</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="K50" t="n">
@@ -9447,13 +9459,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9480,7 +9492,7 @@
       <c r="I51" t="n">
         <v>-0.5664652567975825</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="K51" t="n">
@@ -9493,13 +9505,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9526,7 +9538,7 @@
       <c r="I52" t="n">
         <v>-0.2567975830815704</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="K52" t="n">
@@ -9539,13 +9551,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9572,7 +9584,7 @@
       <c r="I53" t="n">
         <v>-0.2265861027190327</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="K53" t="n">
@@ -9585,13 +9597,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9618,7 +9630,7 @@
       <c r="I54" t="n">
         <v>0.09818731117824819</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="K54" t="n">
@@ -9631,13 +9643,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44608</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9664,7 +9676,7 @@
       <c r="I55" t="n">
         <v>2.084592145015106</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44608</v>
       </c>
       <c r="K55" t="n">
@@ -9677,13 +9689,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44684</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9710,7 +9722,7 @@
       <c r="I56" t="n">
         <v>1.949093655589124</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44684</v>
       </c>
       <c r="K56" t="n">
@@ -9723,13 +9735,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9756,7 +9768,7 @@
       <c r="I57" t="n">
         <v>2.350483383685801</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="K57" t="n">
@@ -9769,13 +9781,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9802,7 +9814,7 @@
       <c r="I58" t="n">
         <v>2.531148036253777</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="K58" t="n">
@@ -9815,13 +9827,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44970</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9848,7 +9860,7 @@
       <c r="I59" t="n">
         <v>-1.129999999999999</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44970</v>
       </c>
       <c r="K59" t="n">
@@ -9861,13 +9873,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9894,7 +9906,7 @@
       <c r="I60" t="n">
         <v>-1.209999999999999</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="K60" t="n">
@@ -9907,13 +9919,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9940,7 +9952,7 @@
       <c r="I61" t="n">
         <v>-1.159999999999999</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="K61" t="n">
@@ -9953,13 +9965,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9986,7 +9998,7 @@
       <c r="I62" t="n">
         <v>-1.479999999999999</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="K62" t="n">
@@ -9999,13 +10011,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10032,7 +10044,7 @@
       <c r="I63" t="n">
         <v>1.97</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="K63" t="n">
@@ -10045,13 +10057,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10078,7 +10090,7 @@
       <c r="I64" t="n">
         <v>1.87</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="K64" t="n">
@@ -10091,13 +10103,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10124,7 +10136,7 @@
       <c r="I65" t="n">
         <v>1.75</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="K65" t="n">
@@ -10137,13 +10149,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45594</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10170,7 +10182,7 @@
       <c r="I66" t="n">
         <v>1.24</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45594</v>
       </c>
       <c r="K66" t="n">
@@ -10183,13 +10195,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10216,7 +10228,7 @@
       <c r="I67" t="n">
         <v>1.49</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="K67" t="n">
@@ -10229,13 +10241,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10262,7 +10274,7 @@
       <c r="I68" t="n">
         <v>1.63</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="K68" t="n">
@@ -10275,13 +10287,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10308,7 +10320,7 @@
       <c r="I69" t="n">
         <v>1.76</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="K69" t="n">
@@ -10321,13 +10333,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10354,7 +10366,7 @@
       <c r="I70" t="n">
         <v>3.080000000000001</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="K70" t="n">
@@ -10367,13 +10379,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46062</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10400,7 +10412,7 @@
       <c r="I71" t="n">
         <v>3.04</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46062</v>
       </c>
       <c r="K71" t="n">
@@ -10413,13 +10425,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46139</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10446,7 +10458,7 @@
       <c r="I72" t="n">
         <v>2.970000000000001</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46139</v>
       </c>
       <c r="K72" t="n">
@@ -10459,13 +10471,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46225</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10492,7 +10504,7 @@
       <c r="I73" t="n">
         <v>3.010000000000001</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46225</v>
       </c>
       <c r="K73" t="n">
@@ -10529,52 +10541,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40030</v>
       </c>
       <c r="C2" t="n">
@@ -10603,10 +10615,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40117</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40122</v>
       </c>
       <c r="C3" t="n">
@@ -10635,10 +10647,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40234</v>
       </c>
       <c r="C4" t="n">
@@ -10667,10 +10679,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40298</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40304</v>
       </c>
       <c r="C5" t="n">
@@ -10699,10 +10711,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40390</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="C6" t="n">
@@ -10731,10 +10743,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40482</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="C7" t="n">
@@ -10763,10 +10775,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40662</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="C8" t="n">
@@ -10795,10 +10807,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40753</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="C9" t="n">
@@ -10827,10 +10839,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40847</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="C10" t="n">
@@ -10859,10 +10871,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="C11" t="n">
@@ -10891,10 +10903,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41029</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41033</v>
       </c>
       <c r="C12" t="n">
@@ -10923,10 +10935,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41121</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41124</v>
       </c>
       <c r="C13" t="n">
@@ -10955,10 +10967,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41213</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="C14" t="n">
@@ -10987,10 +10999,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41325</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="C15" t="n">
@@ -11019,10 +11031,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41394</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41397</v>
       </c>
       <c r="C16" t="n">
@@ -11051,10 +11063,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41488</v>
       </c>
       <c r="C17" t="n">
@@ -11083,10 +11095,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41578</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="C18" t="n">
@@ -11115,10 +11127,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41684</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41691</v>
       </c>
       <c r="C19" t="n">
@@ -11147,10 +11159,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41759</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41761</v>
       </c>
       <c r="C20" t="n">
@@ -11179,10 +11191,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41851</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="C21" t="n">
@@ -11211,10 +11223,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41943</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41953</v>
       </c>
       <c r="C22" t="n">
@@ -11243,10 +11255,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42048</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="C23" t="n">
@@ -11275,10 +11287,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42124</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42129</v>
       </c>
       <c r="C24" t="n">
@@ -11307,10 +11319,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42216</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42223</v>
       </c>
       <c r="C25" t="n">
@@ -11339,10 +11351,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42308</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42314</v>
       </c>
       <c r="C26" t="n">
@@ -11371,10 +11383,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42410</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42418</v>
       </c>
       <c r="C27" t="n">
@@ -11403,10 +11415,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42490</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="C28" t="n">
@@ -11435,10 +11447,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42582</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42586</v>
       </c>
       <c r="C29" t="n">
@@ -11467,10 +11479,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42674</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="C30" t="n">
@@ -11499,10 +11511,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42776</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42783</v>
       </c>
       <c r="C31" t="n">
@@ -11531,10 +11543,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42855</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="C32" t="n">
@@ -11563,10 +11575,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42947</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="C33" t="n">
@@ -11595,10 +11607,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43039</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43042</v>
       </c>
       <c r="C34" t="n">
@@ -11627,10 +11639,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43140</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43151</v>
       </c>
       <c r="C35" t="n">
@@ -11659,10 +11671,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43220</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="C36" t="n">
@@ -11691,10 +11703,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43312</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="C37" t="n">
@@ -11723,10 +11735,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43404</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43406</v>
       </c>
       <c r="C38" t="n">
@@ -11755,10 +11767,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43508</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43516</v>
       </c>
       <c r="C39" t="n">
@@ -11787,10 +11799,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43585</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43591</v>
       </c>
       <c r="C40" t="n">
@@ -11819,10 +11831,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43677</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43682</v>
       </c>
       <c r="C41" t="n">
@@ -11851,10 +11863,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43769</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43774</v>
       </c>
       <c r="C42" t="n">
@@ -11883,10 +11895,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43873</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43881</v>
       </c>
       <c r="C43" t="n">
@@ -11915,10 +11927,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43951</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="C44" t="n">
@@ -11947,10 +11959,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44043</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="C45" t="n">
@@ -11979,10 +11991,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44135</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="C46" t="n">
@@ -12011,10 +12023,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44239</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="C47" t="n">
@@ -12043,10 +12055,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44316</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="C48" t="n">
@@ -12075,10 +12087,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44407</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="C49" t="n">
@@ -12107,10 +12119,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44498</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="C50" t="n">
@@ -12139,10 +12151,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44603</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44608</v>
       </c>
       <c r="C51" t="n">
@@ -12171,10 +12183,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44678</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44684</v>
       </c>
       <c r="C52" t="n">
@@ -12203,10 +12215,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44770</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="C53" t="n">
@@ -12235,10 +12247,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44865</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="C54" t="n">
@@ -12267,10 +12279,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44965</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44970</v>
       </c>
       <c r="C55" t="n">
@@ -12299,10 +12311,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45041</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="C56" t="n">
@@ -12331,10 +12343,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45131</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="C57" t="n">
@@ -12363,10 +12375,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45224</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="C58" t="n">
@@ -12395,10 +12407,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45329</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="C59" t="n">
@@ -12427,10 +12439,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45407</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="C60" t="n">
@@ -12459,10 +12471,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45491</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="C61" t="n">
@@ -12491,10 +12503,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45589</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45594</v>
       </c>
       <c r="C62" t="n">
@@ -12523,10 +12535,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="C63" t="n">
@@ -12555,10 +12567,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45771</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="C64" t="n">
@@ -12587,10 +12599,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45859</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="C65" t="n">
@@ -12619,10 +12631,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45951</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="C66" t="n">
@@ -12651,10 +12663,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46050</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46062</v>
       </c>
       <c r="C67" t="n">
@@ -12683,10 +12695,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46139</v>
       </c>
       <c r="C68" t="n">
@@ -12715,10 +12727,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46219</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46225</v>
       </c>
       <c r="C69" t="n">
@@ -12765,12 +12777,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/T.xlsx
+++ b/salidas/empresas/T.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>4.698482513427734</v>
+        <v>4.698483467102051</v>
       </c>
       <c r="C2" t="n">
         <v>19.59969711303711</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>4.895837306976318</v>
+        <v>4.89583683013916</v>
       </c>
       <c r="C4" t="n">
         <v>20.42296028137207</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>4.824068069458008</v>
+        <v>4.824070930480957</v>
       </c>
       <c r="C5" t="n">
         <v>19.79607391357422</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>4.796462059020996</v>
+        <v>4.796461582183838</v>
       </c>
       <c r="C6" t="n">
         <v>19.68277931213379</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>5.133283138275146</v>
+        <v>5.133281707763672</v>
       </c>
       <c r="C7" t="n">
         <v>21.06495475769043</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>5.821617126464844</v>
+        <v>5.821616649627686</v>
       </c>
       <c r="C9" t="n">
         <v>23.5120849609375</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>6.089038372039795</v>
+        <v>6.089041709899902</v>
       </c>
       <c r="C10" t="n">
         <v>24.5921459197998</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>6.492571353912354</v>
+        <v>6.492570877075195</v>
       </c>
       <c r="C11" t="n">
         <v>25.86857986450195</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>6.428120136260986</v>
+        <v>6.428122997283936</v>
       </c>
       <c r="C12" t="n">
         <v>25.61178207397461</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>6.776917934417725</v>
+        <v>6.776917457580566</v>
       </c>
       <c r="C13" t="n">
         <v>27.00151062011719</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>7.233410835266113</v>
+        <v>7.233414173126221</v>
       </c>
       <c r="C14" t="n">
         <v>28.42144966125488</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>7.579416275024414</v>
+        <v>7.579418182373047</v>
       </c>
       <c r="C16" t="n">
         <v>29.78096771240234</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>7.533193111419678</v>
+        <v>7.53319263458252</v>
       </c>
       <c r="C17" t="n">
         <v>29.24471282958984</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>8.074057579040527</v>
+        <v>8.074056625366211</v>
       </c>
       <c r="C19" t="n">
         <v>31.34441184997559</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>7.707237243652344</v>
+        <v>7.707237720489502</v>
       </c>
       <c r="C20" t="n">
         <v>29.57703971862793</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>7.846974849700928</v>
+        <v>7.846976280212402</v>
       </c>
       <c r="C21" t="n">
         <v>30.1132926940918</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>8.327198028564453</v>
+        <v>8.327201843261719</v>
       </c>
       <c r="C22" t="n">
         <v>31.9561939239502</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>8.317963600158691</v>
+        <v>8.317966461181641</v>
       </c>
       <c r="C23" t="n">
         <v>31.56344413757324</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>7.605394840240479</v>
+        <v>7.60539436340332</v>
       </c>
       <c r="C24" t="n">
         <v>28.85951614379883</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>8.272187232971191</v>
+        <v>8.272188186645508</v>
       </c>
       <c r="C25" t="n">
         <v>31.38972854614258</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>7.760327816009521</v>
+        <v>7.760329246520996</v>
       </c>
       <c r="C26" t="n">
         <v>29.07099723815918</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>7.022404670715332</v>
+        <v>7.022401809692383</v>
       </c>
       <c r="C27" t="n">
         <v>26.3066463470459</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>7.722021102905273</v>
+        <v>7.72202205657959</v>
       </c>
       <c r="C28" t="n">
         <v>28.92749214172363</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>7.912102699279785</v>
+        <v>7.912099361419678</v>
       </c>
       <c r="C29" t="n">
         <v>29.23715972900391</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>8.155331611633301</v>
+        <v>8.155326843261719</v>
       </c>
       <c r="C30" t="n">
         <v>30.13595199584961</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>6.886041164398193</v>
+        <v>6.886039257049561</v>
       </c>
       <c r="C31" t="n">
         <v>25.44561958312988</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>6.401119232177734</v>
+        <v>6.401122093200684</v>
       </c>
       <c r="C32" t="n">
         <v>23.27039337158203</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>6.646279811859131</v>
+        <v>6.64627742767334</v>
       </c>
       <c r="C33" t="n">
         <v>24.16163063049316</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>5.800690174102783</v>
+        <v>5.800688743591309</v>
       </c>
       <c r="C34" t="n">
         <v>21.08761215209961</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>5.678600788116455</v>
+        <v>5.678601741790771</v>
       </c>
       <c r="C35" t="n">
         <v>20.21903228759766</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>6.05830717086792</v>
+        <v>6.058304786682129</v>
       </c>
       <c r="C36" t="n">
         <v>21.57099723815918</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>6.045577526092529</v>
+        <v>6.045580863952637</v>
       </c>
       <c r="C37" t="n">
         <v>21.52568054199219</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>5.324666976928711</v>
+        <v>5.324667453765869</v>
       </c>
       <c r="C38" t="n">
         <v>18.59516525268555</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>5.140833854675293</v>
+        <v>5.140833377838135</v>
       </c>
       <c r="C39" t="n">
         <v>17.95317268371582</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>5.450106620788574</v>
+        <v>5.450108051300049</v>
       </c>
       <c r="C40" t="n">
         <v>19.03323364257812</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>5.656420707702637</v>
+        <v>5.65641975402832</v>
       </c>
       <c r="C41" t="n">
         <v>19.3504524230957</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>5.473170280456543</v>
+        <v>5.47316837310791</v>
       </c>
       <c r="C42" t="n">
         <v>18.72356414794922</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>5.484211444854736</v>
+        <v>5.484210968017578</v>
       </c>
       <c r="C43" t="n">
         <v>18.76132965087891</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>5.923252582550049</v>
+        <v>5.923250675201416</v>
       </c>
       <c r="C44" t="n">
         <v>19.81117820739746</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>5.882604598999023</v>
+        <v>5.882607460021973</v>
       </c>
       <c r="C45" t="n">
         <v>19.67522621154785</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>6.099394798278809</v>
+        <v>6.099389553070068</v>
       </c>
       <c r="C46" t="n">
         <v>20.40030288696289</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>5.915059566497803</v>
+        <v>5.915058135986328</v>
       </c>
       <c r="C47" t="n">
         <v>19.38821792602539</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>6.207700729370117</v>
+        <v>6.207702159881592</v>
       </c>
       <c r="C48" t="n">
         <v>20.34743118286133</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>6.458864688873291</v>
+        <v>6.458865642547607</v>
       </c>
       <c r="C49" t="n">
         <v>21.17069435119629</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>5.960163116455078</v>
+        <v>5.960166931152344</v>
       </c>
       <c r="C50" t="n">
         <v>19.15407943725586</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>5.830902576446533</v>
+        <v>5.830903053283691</v>
       </c>
       <c r="C51" t="n">
         <v>18.73867034912109</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>6.072978973388672</v>
+        <v>6.072976112365723</v>
       </c>
       <c r="C52" t="n">
         <v>19.51661682128906</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>6.256923675537109</v>
+        <v>6.256924152374268</v>
       </c>
       <c r="C53" t="n">
         <v>19.68277931213379</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>5.807942867279053</v>
+        <v>5.807944297790527</v>
       </c>
       <c r="C55" t="n">
         <v>18.27039337158203</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>6.373301029205322</v>
+        <v>6.373303890228271</v>
       </c>
       <c r="C56" t="n">
         <v>19.5921459197998</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>6.641111850738525</v>
+        <v>6.641107082366943</v>
       </c>
       <c r="C57" t="n">
         <v>20.41540718078613</v>
@@ -1665,7 +1665,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>7.142472267150879</v>
+        <v>7.142471790313721</v>
       </c>
       <c r="C59" t="n">
         <v>21.54078483581543</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>6.959652423858643</v>
+        <v>6.95965576171875</v>
       </c>
       <c r="C60" t="n">
         <v>20.98942565917969</v>
@@ -1740,7 +1740,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>7.025445461273193</v>
+        <v>7.025448322296143</v>
       </c>
       <c r="C62" t="n">
         <v>20.78549766540527</v>
@@ -1765,7 +1765,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>7.244993209838867</v>
+        <v>7.24498987197876</v>
       </c>
       <c r="C63" t="n">
         <v>21.43504524230957</v>
@@ -1790,7 +1790,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>7.814279556274414</v>
+        <v>7.81427526473999</v>
       </c>
       <c r="C64" t="n">
         <v>23.11933517456055</v>
@@ -1819,7 +1819,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>8.094583511352539</v>
+        <v>8.094586372375488</v>
       </c>
       <c r="C65" t="n">
         <v>23.50453186035156</v>
@@ -1848,7 +1848,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>8.209033012390137</v>
+        <v>8.209031105041504</v>
       </c>
       <c r="C66" t="n">
         <v>23.83685874938965</v>
@@ -1877,7 +1877,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>8.170014381408691</v>
+        <v>8.170016288757324</v>
       </c>
       <c r="C67" t="n">
         <v>23.72356414794922</v>
@@ -1906,7 +1906,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>7.750281810760498</v>
+        <v>7.750282287597656</v>
       </c>
       <c r="C68" t="n">
         <v>22.09969711303711</v>
@@ -1935,7 +1935,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>7.543678760528564</v>
+        <v>7.543679714202881</v>
       </c>
       <c r="C69" t="n">
         <v>21.51057434082031</v>
@@ -1964,7 +1964,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>7.554276466369629</v>
+        <v>7.554272651672363</v>
       </c>
       <c r="C70" t="n">
         <v>21.54078483581543</v>
@@ -1993,7 +1993,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>7.922854423522949</v>
+        <v>7.92285680770874</v>
       </c>
       <c r="C71" t="n">
         <v>22.1374626159668</v>
@@ -2022,7 +2022,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>7.833653450012207</v>
+        <v>7.833652496337891</v>
       </c>
       <c r="C72" t="n">
         <v>21.88821792602539</v>
@@ -2051,7 +2051,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>8.17424488067627</v>
+        <v>8.174243927001953</v>
       </c>
       <c r="C73" t="n">
         <v>22.83987808227539</v>
@@ -2080,7 +2080,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>8.105208396911621</v>
+        <v>8.105212211608887</v>
       </c>
       <c r="C74" t="n">
         <v>22.21299171447754</v>
@@ -2109,7 +2109,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>8.430408477783203</v>
+        <v>8.430411338806152</v>
       </c>
       <c r="C75" t="n">
         <v>23.1042308807373</v>
@@ -2167,7 +2167,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>9.24029541015625</v>
+        <v>9.240299224853516</v>
       </c>
       <c r="C77" t="n">
         <v>24.85649490356445</v>
@@ -2196,7 +2196,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>9.594074249267578</v>
+        <v>9.594073295593262</v>
       </c>
       <c r="C78" t="n">
         <v>25.80815696716309</v>
@@ -2225,7 +2225,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>10.01242828369141</v>
+        <v>10.01242733001709</v>
       </c>
       <c r="C79" t="n">
         <v>26.93353462219238</v>
@@ -2254,7 +2254,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>10.8232479095459</v>
+        <v>10.82324886322021</v>
       </c>
       <c r="C80" t="n">
         <v>28.64048385620117</v>
@@ -2283,7 +2283,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>10.45790958404541</v>
+        <v>10.45790386199951</v>
       </c>
       <c r="C81" t="n">
         <v>27.67371559143066</v>
@@ -2341,7 +2341,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>10.02511596679688</v>
+        <v>10.02511501312256</v>
       </c>
       <c r="C83" t="n">
         <v>26.1253776550293</v>
@@ -2370,7 +2370,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>9.891796112060547</v>
+        <v>9.891797065734863</v>
       </c>
       <c r="C84" t="n">
         <v>25.77794647216797</v>
@@ -2399,7 +2399,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>9.770069122314453</v>
+        <v>9.77006721496582</v>
       </c>
       <c r="C85" t="n">
         <v>25.46072578430176</v>
@@ -2428,7 +2428,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>10.2557430267334</v>
+        <v>10.25574111938477</v>
       </c>
       <c r="C86" t="n">
         <v>26.27643585205078</v>
@@ -2457,7 +2457,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>10.58590602874756</v>
+        <v>10.58590888977051</v>
       </c>
       <c r="C87" t="n">
         <v>27.12235641479492</v>
@@ -2486,7 +2486,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>10.81583786010742</v>
+        <v>10.81584072113037</v>
       </c>
       <c r="C88" t="n">
         <v>27.71147918701172</v>
@@ -2544,7 +2544,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>10.47891235351562</v>
+        <v>10.47891139984131</v>
       </c>
       <c r="C90" t="n">
         <v>26.42749214172363</v>
@@ -2602,7 +2602,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>10.74137878417969</v>
+        <v>10.74137783050537</v>
       </c>
       <c r="C92" t="n">
         <v>26.63897323608398</v>
@@ -2631,7 +2631,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>10.30283260345459</v>
+        <v>10.30283355712891</v>
       </c>
       <c r="C93" t="n">
         <v>25.55135917663574</v>
@@ -2660,7 +2660,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>10.29978656768799</v>
+        <v>10.29978466033936</v>
       </c>
       <c r="C94" t="n">
         <v>25.5438060760498</v>
@@ -2689,7 +2689,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>11.22124290466309</v>
+        <v>11.2212438583374</v>
       </c>
       <c r="C95" t="n">
         <v>27.34139060974121</v>
@@ -2718,7 +2718,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>10.91436576843262</v>
+        <v>10.9143648147583</v>
       </c>
       <c r="C96" t="n">
         <v>26.59365653991699</v>
@@ -2747,7 +2747,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>10.89886665344238</v>
+        <v>10.89886379241943</v>
       </c>
       <c r="C97" t="n">
         <v>26.5558910369873</v>
@@ -2776,7 +2776,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>10.51167869567871</v>
+        <v>10.51167774200439</v>
       </c>
       <c r="C98" t="n">
         <v>25.16616249084473</v>
@@ -2805,7 +2805,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>10.07317066192627</v>
+        <v>10.07316875457764</v>
       </c>
       <c r="C99" t="n">
         <v>24.11631393432617</v>
@@ -2834,7 +2834,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>11.06376075744629</v>
+        <v>11.06376171112061</v>
       </c>
       <c r="C100" t="n">
         <v>26.4879150390625</v>
@@ -2863,7 +2863,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>11.45916843414307</v>
+        <v>11.45916652679443</v>
       </c>
       <c r="C101" t="n">
         <v>26.9637451171875</v>
@@ -2892,7 +2892,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>11.38533782958984</v>
+        <v>11.38533592224121</v>
       </c>
       <c r="C102" t="n">
         <v>26.79002952575684</v>
@@ -2921,7 +2921,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>11.35002708435059</v>
+        <v>11.35002994537354</v>
       </c>
       <c r="C103" t="n">
         <v>26.70694923400879</v>
@@ -2950,7 +2950,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>11.62033939361572</v>
+        <v>11.62033748626709</v>
       </c>
       <c r="C104" t="n">
         <v>26.88066482543945</v>
@@ -2979,7 +2979,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>11.41463851928711</v>
+        <v>11.41464138031006</v>
       </c>
       <c r="C105" t="n">
         <v>26.40483474731445</v>
@@ -3008,7 +3008,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>11.50606060028076</v>
+        <v>11.50605964660645</v>
       </c>
       <c r="C106" t="n">
         <v>26.61631393432617</v>
@@ -3037,7 +3037,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>11.57499217987061</v>
+        <v>11.57499504089355</v>
       </c>
       <c r="C107" t="n">
         <v>26.31419944763184</v>
@@ -3066,7 +3066,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>11.75439929962158</v>
+        <v>11.7544002532959</v>
       </c>
       <c r="C108" t="n">
         <v>26.72205352783203</v>
@@ -3095,7 +3095,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>11.15970706939697</v>
+        <v>11.15970230102539</v>
       </c>
       <c r="C109" t="n">
         <v>25.37009048461914</v>
@@ -3124,7 +3124,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>11.14348697662354</v>
+        <v>11.1434850692749</v>
       </c>
       <c r="C110" t="n">
         <v>24.86404800415039</v>
@@ -3182,7 +3182,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>11.05209255218506</v>
+        <v>11.05209159851074</v>
       </c>
       <c r="C112" t="n">
         <v>24.66012191772461</v>
@@ -3211,7 +3211,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>11.94996356964111</v>
+        <v>11.94996166229248</v>
       </c>
       <c r="C113" t="n">
         <v>26.16314125061035</v>
@@ -3240,7 +3240,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>11.91546154022217</v>
+        <v>11.91546440124512</v>
       </c>
       <c r="C114" t="n">
         <v>26.08761215209961</v>
@@ -3298,7 +3298,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>12.19664096832275</v>
+        <v>12.19664001464844</v>
       </c>
       <c r="C116" t="n">
         <v>26.23867034912109</v>
@@ -3327,7 +3327,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>11.65597343444824</v>
+        <v>11.65597057342529</v>
       </c>
       <c r="C117" t="n">
         <v>25.07552909851074</v>
@@ -3356,7 +3356,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>11.43830394744873</v>
+        <v>11.43830680847168</v>
       </c>
       <c r="C118" t="n">
         <v>24.60725021362305</v>
@@ -3385,7 +3385,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>11.98878192901611</v>
+        <v>11.98877906799316</v>
       </c>
       <c r="C119" t="n">
         <v>25.30966758728027</v>
@@ -3414,7 +3414,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>12.04602527618408</v>
+        <v>12.04601764678955</v>
       </c>
       <c r="C120" t="n">
         <v>25.43051338195801</v>
@@ -3443,7 +3443,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>12.31077194213867</v>
+        <v>12.31076908111572</v>
       </c>
       <c r="C121" t="n">
         <v>25.98942565917969</v>
@@ -3501,7 +3501,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>13.46692085266113</v>
+        <v>13.46692180633545</v>
       </c>
       <c r="C123" t="n">
         <v>27.9078540802002</v>
@@ -3530,7 +3530,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>14.27603530883789</v>
+        <v>14.27603054046631</v>
       </c>
       <c r="C124" t="n">
         <v>29.58459281921387</v>
@@ -3559,7 +3559,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>14.38169574737549</v>
+        <v>14.38168811798096</v>
       </c>
       <c r="C125" t="n">
         <v>29.32024192810059</v>
@@ -3588,7 +3588,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>14.50395011901855</v>
+        <v>14.50394344329834</v>
       </c>
       <c r="C126" t="n">
         <v>29.56948661804199</v>
@@ -3617,7 +3617,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>16.00806617736816</v>
+        <v>16.0080623626709</v>
       </c>
       <c r="C127" t="n">
         <v>32.63595199584961</v>
@@ -3646,7 +3646,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>16.27631187438965</v>
+        <v>16.27630996704102</v>
       </c>
       <c r="C128" t="n">
         <v>32.69637680053711</v>
@@ -3704,7 +3704,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>15.26867389678955</v>
+        <v>15.2686767578125</v>
       </c>
       <c r="C130" t="n">
         <v>30.67220497131348</v>
@@ -3733,7 +3733,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>14.05630683898926</v>
+        <v>14.05630397796631</v>
       </c>
       <c r="C131" t="n">
         <v>27.78700828552246</v>
@@ -3762,7 +3762,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>14.75930690765381</v>
+        <v>14.75931358337402</v>
       </c>
       <c r="C132" t="n">
         <v>29.17673683166504</v>
@@ -3791,7 +3791,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>16.24937438964844</v>
+        <v>16.24938201904297</v>
       </c>
       <c r="C133" t="n">
         <v>32.12235641479492</v>
@@ -3820,7 +3820,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>16.3568172454834</v>
+        <v>16.35682106018066</v>
       </c>
       <c r="C134" t="n">
         <v>31.84289932250977</v>
@@ -3878,7 +3878,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>16.12015914916992</v>
+        <v>16.12015724182129</v>
       </c>
       <c r="C136" t="n">
         <v>31.38217544555664</v>
@@ -3907,7 +3907,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>15.61937141418457</v>
+        <v>15.61936950683594</v>
       </c>
       <c r="C137" t="n">
         <v>29.9320240020752</v>
@@ -3936,7 +3936,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>15.18582820892334</v>
+        <v>15.18583011627197</v>
       </c>
       <c r="C138" t="n">
         <v>29.1012077331543</v>
@@ -3965,7 +3965,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>14.87052631378174</v>
+        <v>14.87052822113037</v>
       </c>
       <c r="C139" t="n">
         <v>28.49697875976562</v>
@@ -3990,7 +3990,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>15.63719940185547</v>
+        <v>15.63719654083252</v>
       </c>
       <c r="C140" t="n">
         <v>29.4561939239502</v>
@@ -4015,7 +4015,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>15.01972770690918</v>
+        <v>15.01972961425781</v>
       </c>
       <c r="C141" t="n">
         <v>28.29305076599121</v>
@@ -4040,7 +4040,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>15.70535850524902</v>
+        <v>15.70535945892334</v>
       </c>
       <c r="C142" t="n">
         <v>29.58459281921387</v>
@@ -4065,7 +4065,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>13.71733570098877</v>
+        <v>13.71734046936035</v>
       </c>
       <c r="C143" t="n">
         <v>25.41540718078613</v>
@@ -4090,7 +4090,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>14.83021640777588</v>
+        <v>14.83021354675293</v>
       </c>
       <c r="C144" t="n">
         <v>27.47734069824219</v>
@@ -4140,7 +4140,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>15.53526496887207</v>
+        <v>15.53526878356934</v>
       </c>
       <c r="C146" t="n">
         <v>28.28549766540527</v>
@@ -4165,7 +4165,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>15.05821514129639</v>
+        <v>15.0582160949707</v>
       </c>
       <c r="C147" t="n">
         <v>27.41691780090332</v>
@@ -4223,7 +4223,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>13.82164573669434</v>
+        <v>13.82164478302002</v>
       </c>
       <c r="C149" t="n">
         <v>24.69788551330566</v>
@@ -4252,7 +4252,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>13.66102600097656</v>
+        <v>13.66102504730225</v>
       </c>
       <c r="C150" t="n">
         <v>24.41087532043457</v>
@@ -4310,7 +4310,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>13.79248428344727</v>
+        <v>13.79248237609863</v>
       </c>
       <c r="C152" t="n">
         <v>24.14652633666992</v>
@@ -4339,7 +4339,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>13.77953815460205</v>
+        <v>13.77954196929932</v>
       </c>
       <c r="C153" t="n">
         <v>24.12386703491211</v>
@@ -4368,7 +4368,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>14.48707008361816</v>
+        <v>14.48706912994385</v>
       </c>
       <c r="C154" t="n">
         <v>25.3625373840332</v>
@@ -4397,7 +4397,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>13.4979190826416</v>
+        <v>13.49791717529297</v>
       </c>
       <c r="C155" t="n">
         <v>23.17220497131348</v>
@@ -4426,7 +4426,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>13.74429512023926</v>
+        <v>13.74429225921631</v>
       </c>
       <c r="C156" t="n">
         <v>23.59516525268555</v>
@@ -4455,7 +4455,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>12.5564079284668</v>
+        <v>12.55640602111816</v>
       </c>
       <c r="C157" t="n">
         <v>21.5558910369873</v>
@@ -4484,7 +4484,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>13.51693058013916</v>
+        <v>13.51693153381348</v>
       </c>
       <c r="C158" t="n">
         <v>22.70392608642578</v>
@@ -4513,7 +4513,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>13.99357509613037</v>
+        <v>13.99357414245605</v>
       </c>
       <c r="C159" t="n">
         <v>23.50453186035156</v>
@@ -4542,7 +4542,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>14.10149478912354</v>
+        <v>14.10149383544922</v>
       </c>
       <c r="C160" t="n">
         <v>23.68580055236816</v>
@@ -4571,7 +4571,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>14.21803855895996</v>
+        <v>14.21803379058838</v>
       </c>
       <c r="C161" t="n">
         <v>23.38368606567383</v>
@@ -4600,7 +4600,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>14.04352569580078</v>
+        <v>14.0435266494751</v>
       </c>
       <c r="C162" t="n">
         <v>23.09667778015137</v>
@@ -4629,7 +4629,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>15.38909244537354</v>
+        <v>15.38909435272217</v>
       </c>
       <c r="C163" t="n">
         <v>25.30966758728027</v>
@@ -4658,7 +4658,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>15.95157337188721</v>
+        <v>15.95156955718994</v>
       </c>
       <c r="C164" t="n">
         <v>25.7175235748291</v>
@@ -4687,7 +4687,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>16.51842308044434</v>
+        <v>16.51841926574707</v>
       </c>
       <c r="C165" t="n">
         <v>26.63142013549805</v>
@@ -4716,7 +4716,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>17.72709083557129</v>
+        <v>17.72709274291992</v>
       </c>
       <c r="C166" t="n">
         <v>28.58005905151367</v>
@@ -4745,7 +4745,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>18.36241722106934</v>
+        <v>18.3624153137207</v>
       </c>
       <c r="C167" t="n">
         <v>29.07099723815918</v>
@@ -4861,7 +4861,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>17.10145378112793</v>
+        <v>17.1014575958252</v>
       </c>
       <c r="C171" t="n">
         <v>26.6012077331543</v>
@@ -4919,7 +4919,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>15.14160919189453</v>
+        <v>15.14161109924316</v>
       </c>
       <c r="C173" t="n">
         <v>23.01359558105469</v>
@@ -4948,7 +4948,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>15.33541584014893</v>
+        <v>15.33541202545166</v>
       </c>
       <c r="C174" t="n">
         <v>23.30815696716309</v>
@@ -4977,7 +4977,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>15.02234649658203</v>
+        <v>15.02234268188477</v>
       </c>
       <c r="C175" t="n">
         <v>22.83232688903809</v>
@@ -5006,7 +5006,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>15.03926944732666</v>
+        <v>15.03926753997803</v>
       </c>
       <c r="C176" t="n">
         <v>22.34139060974121</v>
@@ -5035,7 +5035,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>15.15620231628418</v>
+        <v>15.15620517730713</v>
       </c>
       <c r="C177" t="n">
         <v>22.51510620117188</v>
@@ -5064,7 +5064,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>14.49524784088135</v>
+        <v>14.4952507019043</v>
       </c>
       <c r="C178" t="n">
         <v>21.53323364257812</v>
@@ -5122,7 +5122,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>14.97526454925537</v>
+        <v>14.97526550292969</v>
       </c>
       <c r="C180" t="n">
         <v>21.71450233459473</v>
@@ -5151,7 +5151,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>14.98047065734863</v>
+        <v>14.98047256469727</v>
       </c>
       <c r="C181" t="n">
         <v>21.72205352783203</v>
@@ -5180,7 +5180,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>15.26411628723145</v>
+        <v>15.26411056518555</v>
       </c>
       <c r="C182" t="n">
         <v>21.62386703491211</v>
@@ -5209,7 +5209,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>14.86958026885986</v>
+        <v>14.86957836151123</v>
       </c>
       <c r="C183" t="n">
         <v>21.06495475769043</v>
@@ -5236,7 +5236,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>16.13848304748535</v>
+        <v>16.13847923278809</v>
       </c>
       <c r="C184" t="n">
         <v>22.8625373840332</v>
@@ -5263,7 +5263,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>17.12751579284668</v>
+        <v>17.12752151489258</v>
       </c>
       <c r="C185" t="n">
         <v>23.72356414794922</v>
@@ -5290,7 +5290,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>16.04784965515137</v>
+        <v>16.04784774780273</v>
       </c>
       <c r="C186" t="n">
         <v>22.22809791564941</v>
@@ -5344,7 +5344,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>15.66822624206543</v>
+        <v>15.66822242736816</v>
       </c>
       <c r="C188" t="n">
         <v>21.18580055236816</v>
@@ -5371,7 +5371,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>15.31631565093994</v>
+        <v>15.31631469726562</v>
       </c>
       <c r="C189" t="n">
         <v>20.70997047424316</v>
@@ -5425,7 +5425,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>14.47468376159668</v>
+        <v>14.47468280792236</v>
       </c>
       <c r="C191" t="n">
         <v>19.07855033874512</v>
@@ -5452,7 +5452,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>13.08222579956055</v>
+        <v>13.08222389221191</v>
       </c>
       <c r="C192" t="n">
         <v>17.24320220947266</v>
@@ -5481,7 +5481,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>14.09648418426514</v>
+        <v>14.09648323059082</v>
       </c>
       <c r="C193" t="n">
         <v>18.58005905151367</v>
@@ -5510,7 +5510,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>15.00794410705566</v>
+        <v>15.00794982910156</v>
       </c>
       <c r="C194" t="n">
         <v>19.25981903076172</v>
@@ -5539,7 +5539,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>13.94267463684082</v>
+        <v>13.94267559051514</v>
       </c>
       <c r="C195" t="n">
         <v>17.89274978637695</v>
@@ -5568,7 +5568,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>13.9073600769043</v>
+        <v>13.90736198425293</v>
       </c>
       <c r="C196" t="n">
         <v>17.84743118286133</v>
@@ -5626,7 +5626,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>16.8291187286377</v>
+        <v>16.82912445068359</v>
       </c>
       <c r="C198" t="n">
         <v>21.29000091552734</v>
@@ -5655,7 +5655,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>16.56826591491699</v>
+        <v>16.56826972961426</v>
       </c>
       <c r="C199" t="n">
         <v>20.95999908447266</v>
@@ -5684,7 +5684,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>15.04276466369629</v>
+        <v>15.04276752471924</v>
       </c>
       <c r="C200" t="n">
         <v>18.78000068664551</v>
@@ -5713,7 +5713,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>14.04952812194824</v>
+        <v>14.04953002929688</v>
       </c>
       <c r="C201" t="n">
         <v>17.54000091552734</v>
@@ -5742,7 +5742,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>12.28732872009277</v>
+        <v>12.28732776641846</v>
       </c>
       <c r="C202" t="n">
         <v>15.34000015258789</v>
@@ -5771,7 +5771,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>14.86157417297363</v>
+        <v>14.861572265625</v>
       </c>
       <c r="C203" t="n">
         <v>18.22999954223633</v>
@@ -5829,7 +5829,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>15.00831127166748</v>
+        <v>15.0083122253418</v>
       </c>
       <c r="C205" t="n">
         <v>18.40999984741211</v>
@@ -5858,7 +5858,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>16.84595108032227</v>
+        <v>16.845947265625</v>
       </c>
       <c r="C206" t="n">
         <v>20.3700008392334</v>
@@ -5887,7 +5887,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>15.6385326385498</v>
+        <v>15.63853454589844</v>
       </c>
       <c r="C207" t="n">
         <v>18.90999984741211</v>
@@ -5941,7 +5941,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>14.82029914855957</v>
+        <v>14.82030010223389</v>
       </c>
       <c r="C209" t="n">
         <v>17.67000007629395</v>
@@ -5995,7 +5995,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>13.3776912689209</v>
+        <v>13.37769031524658</v>
       </c>
       <c r="C211" t="n">
         <v>15.94999980926514</v>
@@ -6022,7 +6022,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>12.39544677734375</v>
+        <v>12.39544582366943</v>
       </c>
       <c r="C212" t="n">
         <v>14.52000045776367</v>
@@ -6076,7 +6076,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>12.82228660583496</v>
+        <v>12.82228755950928</v>
       </c>
       <c r="C214" t="n">
         <v>15.02000045776367</v>
@@ -6103,7 +6103,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>13.39783668518066</v>
+        <v>13.39783763885498</v>
       </c>
       <c r="C215" t="n">
         <v>15.39999961853027</v>
@@ -6130,7 +6130,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>14.41572570800781</v>
+        <v>14.4157247543335</v>
       </c>
       <c r="C216" t="n">
         <v>16.56999969482422</v>
@@ -6157,7 +6157,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>14.59842300415039</v>
+        <v>14.59842395782471</v>
       </c>
       <c r="C217" t="n">
         <v>16.78000068664551</v>
@@ -6211,7 +6211,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>14.96918964385986</v>
+        <v>14.9691915512085</v>
       </c>
       <c r="C219" t="n">
         <v>16.93000030517578</v>
@@ -6240,7 +6240,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>15.56159210205078</v>
+        <v>15.56159019470215</v>
       </c>
       <c r="C220" t="n">
         <v>17.60000038146973</v>
@@ -6356,7 +6356,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>17.55893516540527</v>
+        <v>17.55893325805664</v>
       </c>
       <c r="C224" t="n">
         <v>19.25</v>
@@ -6385,7 +6385,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>18.15182876586914</v>
+        <v>18.15183067321777</v>
       </c>
       <c r="C225" t="n">
         <v>19.89999961853027</v>
@@ -6414,7 +6414,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>20.06735420227051</v>
+        <v>20.06735229492188</v>
       </c>
       <c r="C226" t="n">
         <v>22</v>
@@ -6443,7 +6443,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>20.82389640808105</v>
+        <v>20.82389450073242</v>
       </c>
       <c r="C227" t="n">
         <v>22.54000091552734</v>
@@ -6501,7 +6501,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>21.03638458251953</v>
+        <v>21.03638076782227</v>
       </c>
       <c r="C229" t="n">
         <v>22.77000045776367</v>
@@ -6530,7 +6530,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>22.20155906677246</v>
+        <v>22.20155715942383</v>
       </c>
       <c r="C230" t="n">
         <v>23.72999954223633</v>
@@ -6559,7 +6559,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>25.64453315734863</v>
+        <v>25.64453506469727</v>
       </c>
       <c r="C231" t="n">
         <v>27.40999984741211</v>
@@ -6675,7 +6675,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>27.36337089538574</v>
+        <v>27.36337280273438</v>
       </c>
       <c r="C235" t="n">
         <v>28.94000053405762</v>
@@ -6762,7 +6762,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>26.96830749511719</v>
+        <v>26.96830940246582</v>
       </c>
       <c r="C238" t="n">
         <v>28.23999977111816</v>
@@ -6849,7 +6849,7 @@
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>23.97680282592773</v>
+        <v>23.9768009185791</v>
       </c>
       <c r="C241" t="n">
         <v>24.84000015258789</v>
